--- a/GDT_RSS_Feed_Gen.xlsx
+++ b/GDT_RSS_Feed_Gen.xlsx
@@ -1,134 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\3. Others\My PJ\11. Telegram Channel\2. RSSFeed\1. GDT RSS Feed\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79399392-3891-4EBE-8A5C-13BCFA393E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C96B5918-FBD1-4E03-998E-5B59295AC664}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FeedLinks" sheetId="3" r:id="rId1"/>
-    <sheet name="BundleLink" sheetId="4" r:id="rId2"/>
+    <sheet name="FeedLinks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BundleLink" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
-  <si>
-    <t>No.</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>RSS Link</t>
-  </si>
-  <si>
-    <t>TAFTAC</t>
-  </si>
-  <si>
-    <t>KICPAA</t>
-  </si>
-  <si>
-    <t>GDT</t>
-  </si>
-  <si>
-    <t>ACAR</t>
-  </si>
-  <si>
-    <t>NTS</t>
-  </si>
-  <si>
-    <t>MEF</t>
-  </si>
-  <si>
-    <t>https://web.facebook.com/cambodiataxation</t>
-  </si>
-  <si>
-    <t>https://web.facebook.com/acarcambodia</t>
-  </si>
-  <si>
-    <t>https://web.facebook.com/NationalTaxSchool</t>
-  </si>
-  <si>
-    <t>https://web.facebook.com/ministry.economy.finance</t>
-  </si>
-  <si>
-    <t>https://web.facebook.com/taftacpage</t>
-  </si>
-  <si>
-    <t>https://web.facebook.com/kicpaaofficial</t>
-  </si>
-  <si>
-    <t>Tax Info Update</t>
-  </si>
-  <si>
-    <t>BundleName</t>
-  </si>
-  <si>
-    <t>GDT Bundle</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>BundleLink</t>
-  </si>
-  <si>
-    <t>Update(MN)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -145,51 +53,110 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F29E0D85-6DD3-4F4A-AA08-4F968917B8CC}" name="Table2" displayName="Table2" ref="A1:D7" totalsRowShown="0">
-  <autoFilter ref="A1:D7" xr:uid="{F29E0D85-6DD3-4F4A-AA08-4F968917B8CC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A1:D7" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:D7"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{488077E8-B116-46D8-AC05-3E4F7773FA90}" name="No."/>
-    <tableColumn id="2" xr3:uid="{92A689DA-73BE-4A74-8FCC-6F2BAB1EEE23}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{6DAF5B3E-F70C-4F7B-8A65-57C2423F4BCF}" name="Link"/>
-    <tableColumn id="4" xr3:uid="{E4319524-10FF-423F-B51A-722A6080F220}" name="RSS Link"/>
+    <tableColumn id="1" name="No."/>
+    <tableColumn id="2" name="Name"/>
+    <tableColumn id="3" name="Link"/>
+    <tableColumn id="4" name="RSS Link"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3832A59F-518D-402B-B3F4-12E7E1926CF0}" name="Table1" displayName="Table1" ref="A1:E2" totalsRowShown="0">
-  <autoFilter ref="A1:E2" xr:uid="{3832A59F-518D-402B-B3F4-12E7E1926CF0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table1" displayName="Table1" ref="A1:E2" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:E2"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{DB6BC0B6-D4FE-4232-AE29-30D27BC589D4}" name="No."/>
-    <tableColumn id="2" xr3:uid="{C7B47507-7FDA-4BDD-8710-AF201CAF5D35}" name="BundleName"/>
-    <tableColumn id="3" xr3:uid="{A8707DF6-A7AD-4EA1-9E5A-1F728E548708}" name="Description"/>
-    <tableColumn id="4" xr3:uid="{30589D41-D2CE-4128-AD7E-76F74CA20856}" name="BundleLink" dataCellStyle="Hyperlink"/>
-    <tableColumn id="5" xr3:uid="{4584BE3C-10D2-43B2-8CC9-25569C0EE71B}" name="Update(MN)"/>
+    <tableColumn id="1" name="No."/>
+    <tableColumn id="2" name="BundleName"/>
+    <tableColumn id="3" name="Description"/>
+    <tableColumn id="4" name="BundleLink" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" name="Update(MN)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -457,166 +424,248 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D296AFDD-9753-47B8-A13C-B62D2D7F6292}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.140625" customWidth="1"/>
+    <col width="6.28515625" customWidth="1" min="1" max="1"/>
+    <col width="11.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="50" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="73.140625" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>RSS Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GDT</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>https://web.facebook.com/cambodiataxation</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>https://yamthouchhing.github.io/GDTRSS/feeds/gdt.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ACAR</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>https://web.facebook.com/acarcambodia</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>https://yamthouchhing.github.io/GDTRSS/feeds/acar.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTS</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>https://web.facebook.com/NationalTaxSchool</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>https://yamthouchhing.github.io/GDTRSS/feeds/nts.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MEF</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>https://web.facebook.com/ministry.economy.finance</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>https://yamthouchhing.github.io/GDTRSS/feeds/mef.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TAFTAC</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>https://web.facebook.com/taftacpage</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>https://yamthouchhing.github.io/GDTRSS/feeds/taftac.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KICPAA</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>https://web.facebook.com/kicpaaofficial</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>https://yamthouchhing.github.io/GDTRSS/feeds/kicpaa.xml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{C4B147B6-38E9-44F7-9A2B-82063C451EA4}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{575F9DD8-63F8-42FE-9BE2-7BA0C432D1FD}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{CBD05937-B7F7-4093-B4C9-89336EFB2E63}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{B05FDD1D-4ADC-4C0B-96C5-4CCAEAD06697}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{59C82EF1-2AB9-4E7B-A90D-0FB350120D57}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{0F3C6800-F421-421E-A91A-1C42C83B5448}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9C34A6-A764-4651-B31C-BD6021A830E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" customWidth="1"/>
-    <col min="4" max="4" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col width="6.28515625" customWidth="1" min="1" max="1"/>
+    <col width="14.7109375" customWidth="1" min="2" max="2"/>
+    <col width="15.28515625" customWidth="1" min="3" max="3"/>
+    <col width="41.140625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="13.42578125" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>BundleName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>BundleLink</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Update(MN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GDT Bundle</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tax Info Update</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>https://yamthouchhing.github.io/GDTRSS/feeds/bundle.xml</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>120</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>